--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,17 +498,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,17 +550,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,17 +810,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,17 +914,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,17 +966,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA_BANDA_DE_SHILCAYO</t>
+          <t>LA BANDA DE SHILCAYO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>0094</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.498857</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.35611299999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1863</v>
-      </c>
-      <c r="J2" t="n">
-        <v>79</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.498857</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.356113</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1863</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>0095</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.5253</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.30249999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>345</v>
-      </c>
-      <c r="J3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.5253</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.3025</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>304</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.4928</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.3571</v>
-      </c>
-      <c r="I4" t="n">
-        <v>294</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.4928</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.3571</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>CLEOFE AREVALO DEL AGUILA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.489708</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.350936</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2069</v>
-      </c>
-      <c r="J5" t="n">
-        <v>82</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.489708</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.350936</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>0096</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.5313</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.34610000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>378</v>
-      </c>
-      <c r="J6" t="n">
-        <v>17</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.5313</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.3461</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>0523 / 0523 LUISA DEL CARMEN DEL AGUILA SANCHEZ</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.49702</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.34201</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1039</v>
-      </c>
-      <c r="J7" t="n">
-        <v>47</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.49702</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.34201</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>VIRGEN DOLOROSA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.506379</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.357016</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1341</v>
-      </c>
-      <c r="J8" t="n">
-        <v>67</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.506379</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.357016</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>292</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.4845</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.3472</v>
-      </c>
-      <c r="I9" t="n">
-        <v>441</v>
-      </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.4845</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.3472</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>303</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.49567</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.33882</v>
-      </c>
-      <c r="I10" t="n">
-        <v>334</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.49567</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.33882</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.489963</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.34048199999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>452</v>
-      </c>
-      <c r="J11" t="n">
-        <v>20</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.489963</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.340482</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>483121</t>
+          <t>483164</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0094</t>
+          <t>304</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.498857</t>
+          <t>-6.4928</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.356113</t>
+          <t>-76.3571</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>483135</t>
+          <t>483201</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.5253</t>
+          <t>-6.5313</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.3025</t>
+          <t>-76.3461</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>378</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>483164</t>
+          <t>857592</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>303</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.4928</t>
+          <t>-6.49567</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.3571</t>
+          <t>-76.33882</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>483178</t>
+          <t>527304</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CLEOFE AREVALO DEL AGUILA</t>
+          <t>292</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.489708</t>
+          <t>-6.4845</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.350936</t>
+          <t>-76.3472</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>441</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>483201</t>
+          <t>999450</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.5313</t>
+          <t>-6.489963</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.3461</t>
+          <t>-76.340482</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>452</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>483239</t>
+          <t>483135</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0523 / 0523 LUISA DEL CARMEN DEL AGUILA SANCHEZ</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.49702</t>
+          <t>-6.5253</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.34201</t>
+          <t>-76.3025</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>483296</t>
+          <t>483239</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VIRGEN DOLOROSA</t>
+          <t>0523 / 0523 LUISA DEL CARMEN DEL AGUILA SANCHEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.506379</t>
+          <t>-6.49702</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.357016</t>
+          <t>-76.34201</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>527304</t>
+          <t>483296</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>VIRGEN DOLOROSA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.4845</t>
+          <t>-6.506379</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.3472</t>
+          <t>-76.357016</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>857592</t>
+          <t>483121</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>0094</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.49567</t>
+          <t>-6.498857</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.33882</t>
+          <t>-76.356113</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>999450</t>
+          <t>483178</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>CLEOFE AREVALO DEL AGUILA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.489963</t>
+          <t>-6.489708</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.340482</t>
+          <t>-76.350936</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">

--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>483164</t>
+          <t>999450</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.4928</t>
+          <t>452</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.3571</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-6.489963</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.340482</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>483201</t>
+          <t>857592</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>303</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.5313</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.3461</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>-6.49567</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.33882</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>857592</t>
+          <t>527304</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>292</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.49567</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.33882</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-6.4845</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.3472</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>527304</t>
+          <t>483296</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>VIRGEN DOLOROSA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.4845</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.3472</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>-6.506379</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.357016</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>999450</t>
+          <t>483239</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>0523 / 0523 LUISA DEL CARMEN DEL AGUILA SANCHEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.489963</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.340482</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>-6.49702</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.34201</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>483135</t>
+          <t>483201</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.5253</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.3025</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-6.5313</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.3461</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>483239</t>
+          <t>483178</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0523 / 0523 LUISA DEL CARMEN DEL AGUILA SANCHEZ</t>
+          <t>CLEOFE AREVALO DEL AGUILA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.49702</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.34201</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>-6.489708</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-76.350936</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>483296</t>
+          <t>483164</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VIRGEN DOLOROSA</t>
+          <t>304</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.506379</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.357016</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>-6.4928</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-76.3571</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>483121</t>
+          <t>483135</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0094</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.498857</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.356113</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>-6.5253</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-76.3025</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>483178</t>
+          <t>483121</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CLEOFE AREVALO DEL AGUILA</t>
+          <t>0094</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.489708</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.350936</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>-6.498857</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-76.356113</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">

--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-LA_BANDA_DE_SHILCAYO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
